--- a/ELW2025/ELW2025_発表論文公開承諾書.xlsx
+++ b/ELW2025/ELW2025_発表論文公開承諾書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ninjal-my.sharepoint.com/personal/masayu-a_ninjal_ac_jp/Documents/デスクトップ/ELW/ELW2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ninjal-my.sharepoint.com/personal/masayu-a_ninjal_ac_jp/Documents/ドキュメント/GitHub/ELW/ELW2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F423B50-52D3-4C84-85F2-5938D0B73B13}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6225FD2A-125B-472B-80D7-EEBAA46A84C0}"/>
   <bookViews>
-    <workbookView xWindow="-76910" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="2070" windowWidth="16200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="論文メタデータ" sheetId="1" r:id="rId1"/>
@@ -182,7 +182,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Evidence-based Linguistics Workshop 2024 に投稿した以下の発表論文について、以下の扱いを承諾する。
+    <t>Evidence-based Linguistics Workshop 2025 に投稿した以下の発表論文について、以下の扱いを承諾する。
 ・論文の著作権は著者に帰属する
 ・著者は、同論文をクリエイティブコモンズ 4.0 表示 (CC BY 4.0) のもと、国立国語研究所が国立国語研究所機関リポジトリにて公開することを許諾する
 ・国立国語研究所の機関リポジトリ登録にともない、抄録を含めた同論文のメタデータの自由利用（複製、翻訳、再配布等）を認める</t>
@@ -849,6 +849,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Invited_Students xmlns="e56da3c0-a9e1-42c3-99ce-a9b98a1dde41" xsi:nil="true"/>
@@ -892,15 +901,6 @@
     </Student_Groups>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1287,6 +1287,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72F3867-CC1F-439F-86D6-7D75107B8029}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -1299,14 +1307,6 @@
     <ds:schemaRef ds:uri="e56da3c0-a9e1-42c3-99ce-a9b98a1dde41"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ELW2025/ELW2025_発表論文公開承諾書.xlsx
+++ b/ELW2025/ELW2025_発表論文公開承諾書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ninjal-my.sharepoint.com/personal/masayu-a_ninjal_ac_jp/Documents/デスクトップ/ELW/ELW2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ninjal-my.sharepoint.com/personal/masayu-a_ninjal_ac_jp/Documents/ドキュメント/GitHub/ELW/ELW2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F423B50-52D3-4C84-85F2-5938D0B73B13}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{196F84EF-70A3-49E7-B381-181E13B0FFC8}"/>
   <bookViews>
-    <workbookView xWindow="-76910" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="2070" windowWidth="16200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="論文メタデータ" sheetId="1" r:id="rId1"/>
@@ -182,7 +182,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Evidence-based Linguistics Workshop 2024 に投稿した以下の発表論文について、以下の扱いを承諾する。
+    <t>Evidence-based Linguistics Workshop 2025 に投稿した以下の発表論文について、以下の扱いを承諾する。
 ・論文の著作権は著者に帰属する
 ・著者は、同論文をクリエイティブコモンズ 4.0 表示 (CC BY 4.0) のもと、国立国語研究所が国立国語研究所機関リポジトリにて公開することを許諾する
 ・国立国語研究所の機関リポジトリ登録にともない、抄録を含めた同論文のメタデータの自由利用（複製、翻訳、再配布等）を認める</t>
@@ -895,15 +895,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010084F48AE92D7C994BA1FFFB5EC0217B44" ma:contentTypeVersion="29" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c1ece492b088b728ddc229bb90f269bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f3f512d3-6195-4655-8eda-4b4a84e395f6" xmlns:ns4="e56da3c0-a9e1-42c3-99ce-a9b98a1dde41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e11460e12859cbbd19c5a12eafaba3f" ns3:_="" ns4:_="">
     <xsd:import namespace="f3f512d3-6195-4655-8eda-4b4a84e395f6"/>
@@ -1286,6 +1277,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72F3867-CC1F-439F-86D6-7D75107B8029}">
   <ds:schemaRefs>
@@ -1304,14 +1304,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5C0875-96D2-40B8-96FC-BBC6F745AEF0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1328,4 +1320,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ELW2025/ELW2025_発表論文公開承諾書.xlsx
+++ b/ELW2025/ELW2025_発表論文公開承諾書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ninjal-my.sharepoint.com/personal/masayu-a_ninjal_ac_jp/Documents/ドキュメント/GitHub/ELW/ELW2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{196F84EF-70A3-49E7-B381-181E13B0FFC8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6225FD2A-125B-472B-80D7-EEBAA46A84C0}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="2070" windowWidth="16200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -849,6 +849,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Invited_Students xmlns="e56da3c0-a9e1-42c3-99ce-a9b98a1dde41" xsi:nil="true"/>
@@ -894,7 +903,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010084F48AE92D7C994BA1FFFB5EC0217B44" ma:contentTypeVersion="29" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c1ece492b088b728ddc229bb90f269bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f3f512d3-6195-4655-8eda-4b4a84e395f6" xmlns:ns4="e56da3c0-a9e1-42c3-99ce-a9b98a1dde41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e11460e12859cbbd19c5a12eafaba3f" ns3:_="" ns4:_="">
     <xsd:import namespace="f3f512d3-6195-4655-8eda-4b4a84e395f6"/>
@@ -1277,16 +1286,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72F3867-CC1F-439F-86D6-7D75107B8029}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -1303,7 +1311,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5C0875-96D2-40B8-96FC-BBC6F745AEF0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1320,12 +1328,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>